--- a/artfynd/A 39028-2026 artfynd.xlsx
+++ b/artfynd/A 39028-2026 artfynd.xlsx
@@ -1013,6 +1013,11 @@
           <t>2026-10-02</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Enstaka lockläten 2 av 6 dagar</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39028-2026 artfynd.xlsx
+++ b/artfynd/A 39028-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137322211</v>
       </c>
       <c r="B2" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>137323065</v>
       </c>
       <c r="B3" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137322376</v>
       </c>
       <c r="B4" t="n">
-        <v>58577</v>
+        <v>58579</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>137322001</v>
       </c>
       <c r="B5" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>137322829</v>
       </c>
       <c r="B6" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39028-2026 artfynd.xlsx
+++ b/artfynd/A 39028-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137322211</v>
       </c>
       <c r="B2" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>137323065</v>
       </c>
       <c r="B3" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137322376</v>
       </c>
       <c r="B4" t="n">
-        <v>58579</v>
+        <v>58581</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>137322001</v>
       </c>
       <c r="B5" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>137322829</v>
       </c>
       <c r="B6" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 39028-2026 artfynd.xlsx
+++ b/artfynd/A 39028-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137322211</v>
       </c>
       <c r="B2" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>137323065</v>
       </c>
       <c r="B3" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -931,7 +931,7 @@
         <v>137322376</v>
       </c>
       <c r="B4" t="n">
-        <v>58581</v>
+        <v>58584</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1055,7 +1055,7 @@
         <v>137322001</v>
       </c>
       <c r="B5" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1179,7 +1179,7 @@
         <v>137322829</v>
       </c>
       <c r="B6" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
